--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2023_coquimbo.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2023_coquimbo.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:06</t>
+    <t xml:space="preserve">2026-09-09 21:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2023_coquimbo.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2023_coquimbo.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:13</t>
+    <t xml:space="preserve">2026-09-18 09:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2023_coquimbo.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2023_coquimbo.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:05</t>
+    <t xml:space="preserve">2026-09-25 21:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -477,7 +477,7 @@
         <v>1302498.25</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>329638.63</v>
+        <v>329638.62</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2023_coquimbo.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_i_ingr_a_2023_coquimbo.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 21:28</t>
+    <t xml:space="preserve">2026-10-05 02:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -471,13 +471,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>972859.62</v>
+        <v>972859.63</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1302498.25</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>329638.62</v>
+        <v>329638.63</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +620,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1063061.12</v>
+        <v>1063061.13</v>
       </c>
     </row>
   </sheetData>
